--- a/dws-pipeline-analyzer/templates/变更清单_示例.xlsx
+++ b/dws-pipeline-analyzer/templates/变更清单_示例.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,10 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +135,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>表级变化类型：表/视图下线、表/视图替换、表/视图主键变化、表/视图名称或者schema变化、平切、表/视图数据初始化（刷时间戳）、表/视图初始化（不刷时间戳）、表/视图数据归档、表/视图取消权限、表/视图数据硬删除</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>字段变化类型：字段类型及长度变化、字段下线/删除、字段值语义变化、新增字段、字段名称变化、字段数据初始化（刷时间戳）、字段数据初始化（不刷时间戳）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>类型说明（可选）：补充每个变化类型的详细定义</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,8 +471,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -462,47 +508,94 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ods.user_info_src</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ods_new.user_info</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>用户表平切</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>平切</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>表级变化类型：表/视图下线、表/视图替换、表/视图主键变化、表/视图名称或者schema变化、平切、表/视图数据初始化（刷时间戳）、表/视图初始化（不刷时间戳）、表/视图数据归档、表/视图取消权限、表/视图数据硬删除</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ods.order_log_src</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>日志表整表下线</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>表/视图下线</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ods.user_info_src</t>
+          <t>ods.product_src</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ods_new.user_info</t>
+          <t>ods_new.product</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>用户表平切</t>
+          <t>表名变更</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>平切</t>
+          <t>表/视图名称或者schema变化</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ods.order_log_src</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>ods.config_src</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ods_new.config</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>N</t>
@@ -510,64 +603,10 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>日志表整表下线</t>
+          <t>数据初始化</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>表/视图下线</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ods.product_src</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ods_new.product</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>表名变更</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>表/视图名称或者schema变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ods.config_src</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ods_new.config</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>数据初始化</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>表/视图初始化（不刷时间戳）</t>
         </is>
@@ -575,6 +614,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -584,8 +624,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -679,16 +739,161 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ods</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>user_info_src</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ods_new</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>user_info</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>字段类型及长度变化</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CAST兼容，无需还原</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>字段变化类型：字段类型及长度变化、字段下线/删除、字段值语义变化、新增字段、字段名称变化、字段数据初始化（刷时间戳）、字段数据初始化（不刷时间戳）</t>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ods</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>user_info_src</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>old_status</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>旧状态</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>字段下线/删除</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>李四</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -707,17 +912,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>用户ID</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -737,32 +942,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>用户ID</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>字段类型及长度变化</t>
+          <t>字段值语义变化</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CAST兼容，无需还原</t>
+          <t>状态码从0/1改为A/B/C</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -778,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -797,222 +1002,70 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>old_status</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>旧状态</t>
+          <t>手机号</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ods_new</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>user_info</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>字段下线/删除</t>
+          <t>字段名称变化</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>引用处改字段名即可</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>user_info_src</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ods_new</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>user_info</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>字段值语义变化</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>状态码从0/1改为A/B/C</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ods</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>user_info_src</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>手机号</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ods_new</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>user_info</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>手机号</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>字段名称变化</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>引用处改字段名即可</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
@@ -1020,6 +1073,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1029,8 +1083,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1044,212 +1102,205 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>字段类型及长度变化</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>字段的数据类型或长度发生变化，需检查下游cast/转换是否兼容</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>类型说明（可选）：补充每个变化类型的详细定义</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>字段下线/删除</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>字段被废弃删除，下游取不到该数据</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>字段类型及长度变化</t>
+          <t>字段值语义变化</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>字段的数据类型或长度发生变化，需检查下游cast/转换是否兼容</t>
+          <t>字段名和类型不变，但值的含义变了（如状态码含义改变）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>字段下线/删除</t>
+          <t>新增字段</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>字段被废弃删除，下游取不到该数据</t>
+          <t>源端新增字段，下游一般无影响（未引用）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>字段值语义变化</t>
+          <t>字段名称变化</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>字段名和类型不变，但值的含义变了（如状态码含义改变）</t>
+          <t>字段重命名，数据不变但引用处需改名</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新增字段</t>
+          <t>字段数据初始化（刷时间戳）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>源端新增字段，下游一般无影响（未引用）</t>
+          <t>数据被重新初始化并更新时间戳，增量下游会重新拉取</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>字段名称变化</t>
+          <t>字段数据初始化（不刷时间戳）</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>字段重命名，数据不变但引用处需改名</t>
+          <t>数据被重新初始化但不更新时间戳，增量下游可能漏拉</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>字段数据初始化（刷时间戳）</t>
+          <t>表/视图下线</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>数据被重新初始化并更新时间戳，增量下游会重新拉取</t>
+          <t>整表下线，来源消失</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>字段数据初始化（不刷时间戳）</t>
+          <t>表/视图替换</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>数据被重新初始化但不更新时间戳，增量下游可能漏拉</t>
+          <t>表被替换为另一张表</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>表/视图下线</t>
+          <t>表/视图主键变化</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>整表下线，来源消失</t>
+          <t>主键改变，影响JOIN/去重逻辑</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>表/视图替换</t>
+          <t>表/视图名称或者schema变化</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>表被替换为另一张表</t>
+          <t>表名/schema变了，需改引用+术+规则+调度</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>表/视图主键变化</t>
+          <t>平切</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主键改变，影响JOIN/去重逻辑</t>
+          <t>字段完全一致仅表名变化</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>表/视图名称或者schema变化</t>
+          <t>表/视图数据初始化（刷时间戳）</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>表名/schema变了，需改引用+术+规则+调度</t>
+          <t>整表数据初始化并更新时间戳</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>平切</t>
+          <t>表/视图初始化（不刷时间戳）</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>字段完全一致仅表名变化</t>
+          <t>整表数据初始化但不更新时间戳</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>表/视图数据初始化（刷时间戳）</t>
+          <t>表/视图数据归档</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>整表数据初始化并更新时间戳</t>
+          <t>历史数据归档，需确认是否影响查询</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>表/视图初始化（不刷时间戳）</t>
+          <t>表/视图取消权限</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>整表数据初始化但不更新时间戳</t>
+          <t>权限取消，下游无法访问</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>表/视图数据归档</t>
+          <t>表/视图数据硬删除</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>历史数据归档，需确认是否影响查询</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>表/视图取消权限</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>权限取消，下游无法访问</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>表/视图数据硬删除</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
         <is>
           <t>数据被硬删除</t>
         </is>
@@ -1257,5 +1308,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>